--- a/ANILLOS TOUS.xlsx
+++ b/ANILLOS TOUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2227C78-E935-4578-8721-ED42EF0E6833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB23DB1-7D42-4AA6-82EA-97ACED4F7DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
   <si>
     <t xml:space="preserve">ANILLOS </t>
   </si>
@@ -75,13 +75,13 @@
     <t>TALLAS</t>
   </si>
   <si>
-    <t>6--7--8</t>
-  </si>
-  <si>
     <t>NUMERO</t>
   </si>
   <si>
     <t>PRECIO</t>
+  </si>
+  <si>
+    <t>50-52-54-56-58</t>
   </si>
 </sst>
 </file>
@@ -90,7 +90,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-540A]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -254,7 +254,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -272,12 +272,12 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -309,13 +309,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>209551</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1123951</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>1199666</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -353,13 +353,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>55563</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1246188</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>1206228</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -397,13 +397,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>230187</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>103187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1124638</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>1222375</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -441,13 +441,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1222375</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1215851</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -485,13 +485,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>246062</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1158875</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>1158803</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -517,6 +517,182 @@
         <a:xfrm>
           <a:off x="1722437" y="889000"/>
           <a:ext cx="912813" cy="1063553"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>182562</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1141891</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1158876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C66E49E-1F9F-09FF-768F-3BBB6E0018B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1658937" y="865188"/>
+          <a:ext cx="959329" cy="1087438"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>127001</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>39933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1190627</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1232406</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA282614-3157-C526-A583-C1A29AFFB208}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1603376" y="833683"/>
+          <a:ext cx="1063626" cy="1192473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>198438</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1143001</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1148496</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3EE9B0A-D4B6-8FA3-66CE-C58A2B7975B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1674813" y="873125"/>
+          <a:ext cx="944563" cy="1069121"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>158751</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1246189</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1161508</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F7794CB-DDF8-C377-8CDA-A3796D75D1F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1635126" y="873125"/>
+          <a:ext cx="1087438" cy="1082133"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -825,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:F745"/>
+  <dimension ref="A2:F749"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -838,18 +1014,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="28.5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
@@ -861,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>4</v>
@@ -869,98 +1045,166 @@
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1">
       <c r="A4" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
       </c>
-      <c r="C4" s="13"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="9">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="E4" s="4">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="99.75" customHeight="1">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3">
         <v>10</v>
       </c>
-      <c r="C5" s="12"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="9">
-        <v>5.8</v>
+        <v>6.73</v>
       </c>
       <c r="E5" s="4">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="99.75" customHeight="1">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
         <v>10</v>
       </c>
-      <c r="C6" s="12"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="9">
-        <v>6.39</v>
+        <v>5.83</v>
       </c>
       <c r="E6" s="4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="99.75" customHeight="1">
       <c r="A7" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>10</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="11"/>
       <c r="D7" s="9">
-        <v>6.25</v>
+        <v>5.68</v>
       </c>
       <c r="E7" s="4">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="99.75" customHeight="1">
       <c r="A8" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3">
         <v>10</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="11"/>
       <c r="D8" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>135</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A9" s="2">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9">
+        <v>5.8</v>
+      </c>
+      <c r="E9" s="4">
+        <v>140</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9">
+        <v>6.39</v>
+      </c>
+      <c r="E10" s="4">
+        <v>150</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9">
+        <v>6.25</v>
+      </c>
+      <c r="E11" s="4">
+        <v>145</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9">
         <v>4.1100000000000003</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E12" s="4">
         <v>140</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>5</v>
+      <c r="F12" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="13" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="14" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="15" spans="1:6" ht="15.75" customHeight="1"/>
@@ -1694,23 +1938,31 @@
     <row r="743" ht="15.75" customHeight="1"/>
     <row r="744" ht="15.75" customHeight="1"/>
     <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:F8">
-    <sortCondition descending="1" ref="A8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:F12">
+    <sortCondition descending="1" ref="A12"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D8" r:id="rId1" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D7" r:id="rId2" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{188DE113-632D-4906-AEE0-8FD40F363C09}"/>
-    <hyperlink ref="D6" r:id="rId3" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{92DB168B-99D2-4C2F-AE0E-FD30F85F10D6}"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{2AE8BBE2-B334-4852-AB0C-11245DC86DD4}"/>
-    <hyperlink ref="D4" r:id="rId5" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{4A0E244F-45B9-4005-84F4-D7FDC79985C1}"/>
+    <hyperlink ref="D12" r:id="rId1" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D11" r:id="rId2" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{188DE113-632D-4906-AEE0-8FD40F363C09}"/>
+    <hyperlink ref="D10" r:id="rId3" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{92DB168B-99D2-4C2F-AE0E-FD30F85F10D6}"/>
+    <hyperlink ref="D9" r:id="rId4" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{2AE8BBE2-B334-4852-AB0C-11245DC86DD4}"/>
+    <hyperlink ref="D8" r:id="rId5" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{4A0E244F-45B9-4005-84F4-D7FDC79985C1}"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{91351C30-6AA6-44E1-8742-92BCDC43F8BA}"/>
+    <hyperlink ref="D6" r:id="rId7" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{D1E59488-A251-4B7F-A395-A1A72DE911EA}"/>
+    <hyperlink ref="D5" r:id="rId8" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{DCFA9871-E408-40B5-B1DC-F7BCA577FED3}"/>
+    <hyperlink ref="D4" r:id="rId9" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{DCD5A086-D0BC-4B90-9EE2-58D8645D1743}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup orientation="portrait" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>